--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251108_201527.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
